--- a/Day 4/Guerrilla AI - Day 4 - Demo Start.xlsx
+++ b/Day 4/Guerrilla AI - Day 4 - Demo Start.xlsx
@@ -604,7 +604,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Type each code block into a PY() cell in column E (to the right of the code) and run it. The whole area to the right and below is left open so your results can spill freely.</t>
+          <t xml:space="preserve">Watch live and answer the chat choices. Afterward, try the code in column E. Leave the space to the right and below open for results.</t>
         </is>
       </c>
     </row>
@@ -618,14 +618,14 @@
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Type it, don't paste it.</t>
+          <t xml:space="preserve">Watch now. Try one block later.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>The code is printed here so you never get stuck. But time permitting, type along rather than paste. Typing builds the muscle memory and makes you slow down and understand each line. Paste only if you fall behind.</t>
+          <t xml:space="preserve">No live typing required. Choose NEW or TRIED in chat. If PY is unavailable in your Excel, use the demo to follow the result.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10" ht="21" customHeight="1">
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>xl() hands the SalesClean table to pandas as a DataFrame.</t>
+          <t xml:space="preserve">Python reads SalesClean as a table. You can follow the result without memorizing the code.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
     <row r="25" ht="21" customHeight="1">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>One groupby answers what the pivot took clicks to build.</t>
+          <t xml:space="preserve">Chat check: for total sales, SUM or COUNT? Read the code and choose one.</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
     <row r="38" ht="21" customHeight="1">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Ask a free chatbot for this code, paste it here, run it.</t>
+          <t xml:space="preserve">Chat choice: would you chart SALES or ORDERS? Today we chart sales and check the totals.</t>
         </is>
       </c>
     </row>
@@ -753,14 +753,14 @@
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>✓  Takeaway</t>
+          <t xml:space="preserve">One small next step</t>
         </is>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>You already have a data science environment. The craft is knowing how to ask for the code.</t>
+          <t xml:space="preserve">Pick SUMMARY or CHART. Try one block if PY is available, or follow the demo result.</t>
         </is>
       </c>
     </row>
